--- a/EXCEL/class notes/day12 subs&replace/Slicer.xlsx
+++ b/EXCEL/class notes/day12 subs&replace/Slicer.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Documents\Kamal\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\data-analyst\EXCEL\class notes\day12 subs&amp;replace\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AD47687-D322-432B-BD2A-335B6004921E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F5B17B0-807C-4C74-912A-92A7C4A25D0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{AF9B4C49-C842-4D71-845F-2F2608CB95C0}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{AF9B4C49-C842-4D71-845F-2F2608CB95C0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,15 +20,17 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$1</definedName>
     <definedName name="Slicer_Class">#N/A</definedName>
     <definedName name="Slicer_Class1">#N/A</definedName>
+    <definedName name="Slicer_Result">#N/A</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId3"/>
+    <pivotCache cacheId="1" r:id="rId3"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
       <x14:slicerCaches>
         <x14:slicerCache r:id="rId4"/>
+        <x14:slicerCache r:id="rId5"/>
       </x14:slicerCaches>
     </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
@@ -36,11 +38,20 @@
     </ext>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{46BE6895-7355-4a93-B00E-2C351335B9C9}">
       <x15:slicerCaches xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main">
-        <x14:slicerCache r:id="rId5"/>
+        <x14:slicerCache r:id="rId6"/>
       </x15:slicerCaches>
     </ext>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -121,7 +132,7 @@
     <t>Disctinction</t>
   </si>
   <si>
-    <t>(Multiple Items)</t>
+    <t>(All)</t>
   </si>
 </sst>
 </file>
@@ -294,7 +305,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -334,11 +345,180 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="12">
+  <dxfs count="36">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <numFmt numFmtId="20" formatCode="dd/mmm/yy"/>
       <fill>
@@ -581,25 +761,103 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>165100</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>88900</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>640080</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>7621</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>82550</xdr:colOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>563880</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>171449</xdr:rowOff>
+      <xdr:rowOff>160020</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
-            <xdr:cNvPr id="3" name="Class">
+            <xdr:cNvPr id="2" name="Result">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6A910310-2924-6D08-C273-93D71F26E3EB}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{232C3A41-A7B8-DA1D-4EAD-17891491605F}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
+              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="Result"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="5943600" y="2019301"/>
+              <a:ext cx="1828800" cy="883919"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-IN" sz="1100"/>
+                <a:t>This shape represents a slicer. Slicers are supported in Excel 2010 or later.
+If the shape was modified in an earlier version of Excel, or if the workbook was saved in Excel 2003 or earlier, the slicer cannot be used.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>83820</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>129541</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>99060</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="4" name="Class">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{400B1ABB-59AD-8AD7-AF21-4FAF451587AF}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -626,8 +884,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="6578600" y="1930400"/>
-              <a:ext cx="4146550" cy="1003299"/>
+              <a:off x="8153400" y="1958341"/>
+              <a:ext cx="3116580" cy="1066799"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -672,7 +930,7 @@
     <xdr:to>
       <xdr:col>10</xdr:col>
       <xdr:colOff>590550</xdr:colOff>
-      <xdr:row>29</xdr:row>
+      <xdr:row>17</xdr:row>
       <xdr:rowOff>111125</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
@@ -778,7 +1036,10 @@
       </sharedItems>
     </cacheField>
     <cacheField name="Result" numFmtId="0">
-      <sharedItems/>
+      <sharedItems count="2">
+        <s v="Pass"/>
+        <s v="Fail"/>
+      </sharedItems>
     </cacheField>
     <cacheField name="Date" numFmtId="14">
       <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2024-12-18T00:00:00" maxDate="2024-12-21T00:00:00" count="3">
@@ -803,7 +1064,7 @@
     <s v="Nme1"/>
     <n v="61"/>
     <x v="0"/>
-    <s v="Pass"/>
+    <x v="0"/>
     <x v="0"/>
   </r>
   <r>
@@ -811,7 +1072,7 @@
     <s v="Nme2"/>
     <n v="37"/>
     <x v="1"/>
-    <s v="Pass"/>
+    <x v="0"/>
     <x v="0"/>
   </r>
   <r>
@@ -819,7 +1080,7 @@
     <s v="Nme3"/>
     <n v="12"/>
     <x v="2"/>
-    <s v="Fail"/>
+    <x v="1"/>
     <x v="0"/>
   </r>
   <r>
@@ -827,7 +1088,7 @@
     <s v="Nme4"/>
     <n v="11"/>
     <x v="2"/>
-    <s v="Fail"/>
+    <x v="1"/>
     <x v="0"/>
   </r>
   <r>
@@ -835,7 +1096,7 @@
     <s v="Nme5"/>
     <n v="45"/>
     <x v="1"/>
-    <s v="Pass"/>
+    <x v="0"/>
     <x v="0"/>
   </r>
   <r>
@@ -843,7 +1104,7 @@
     <s v="Nme6"/>
     <n v="6"/>
     <x v="2"/>
-    <s v="Fail"/>
+    <x v="1"/>
     <x v="0"/>
   </r>
   <r>
@@ -851,7 +1112,7 @@
     <s v="Nme7"/>
     <n v="19"/>
     <x v="2"/>
-    <s v="Fail"/>
+    <x v="1"/>
     <x v="0"/>
   </r>
   <r>
@@ -859,7 +1120,7 @@
     <s v="Nme8"/>
     <n v="87"/>
     <x v="3"/>
-    <s v="Pass"/>
+    <x v="0"/>
     <x v="0"/>
   </r>
   <r>
@@ -867,7 +1128,7 @@
     <s v="Nme9"/>
     <n v="43"/>
     <x v="1"/>
-    <s v="Pass"/>
+    <x v="0"/>
     <x v="0"/>
   </r>
   <r>
@@ -875,7 +1136,7 @@
     <s v="Nme10"/>
     <n v="68"/>
     <x v="0"/>
-    <s v="Pass"/>
+    <x v="0"/>
     <x v="0"/>
   </r>
   <r>
@@ -883,7 +1144,7 @@
     <s v="Nme1"/>
     <n v="96"/>
     <x v="3"/>
-    <s v="Pass"/>
+    <x v="0"/>
     <x v="1"/>
   </r>
   <r>
@@ -891,7 +1152,7 @@
     <s v="Nme2"/>
     <n v="87"/>
     <x v="3"/>
-    <s v="Pass"/>
+    <x v="0"/>
     <x v="1"/>
   </r>
   <r>
@@ -899,7 +1160,7 @@
     <s v="Nme3"/>
     <n v="100"/>
     <x v="3"/>
-    <s v="Pass"/>
+    <x v="0"/>
     <x v="1"/>
   </r>
   <r>
@@ -907,7 +1168,7 @@
     <s v="Nme4"/>
     <n v="86"/>
     <x v="3"/>
-    <s v="Pass"/>
+    <x v="0"/>
     <x v="1"/>
   </r>
   <r>
@@ -915,7 +1176,7 @@
     <s v="Nme5"/>
     <n v="85"/>
     <x v="3"/>
-    <s v="Pass"/>
+    <x v="0"/>
     <x v="1"/>
   </r>
   <r>
@@ -923,7 +1184,7 @@
     <s v="Nme6"/>
     <n v="75"/>
     <x v="3"/>
-    <s v="Pass"/>
+    <x v="0"/>
     <x v="1"/>
   </r>
   <r>
@@ -931,7 +1192,7 @@
     <s v="Nme7"/>
     <n v="3"/>
     <x v="2"/>
-    <s v="Fail"/>
+    <x v="1"/>
     <x v="1"/>
   </r>
   <r>
@@ -939,7 +1200,7 @@
     <s v="Nme8"/>
     <n v="100"/>
     <x v="3"/>
-    <s v="Pass"/>
+    <x v="0"/>
     <x v="1"/>
   </r>
   <r>
@@ -947,7 +1208,7 @@
     <s v="Nme9"/>
     <n v="59"/>
     <x v="1"/>
-    <s v="Pass"/>
+    <x v="0"/>
     <x v="1"/>
   </r>
   <r>
@@ -955,7 +1216,7 @@
     <s v="Nme10"/>
     <n v="3"/>
     <x v="2"/>
-    <s v="Fail"/>
+    <x v="1"/>
     <x v="1"/>
   </r>
   <r>
@@ -963,7 +1224,7 @@
     <s v="Nme1"/>
     <n v="47"/>
     <x v="1"/>
-    <s v="Pass"/>
+    <x v="0"/>
     <x v="2"/>
   </r>
   <r>
@@ -971,7 +1232,7 @@
     <s v="Nme2"/>
     <n v="92"/>
     <x v="3"/>
-    <s v="Pass"/>
+    <x v="0"/>
     <x v="2"/>
   </r>
   <r>
@@ -979,7 +1240,7 @@
     <s v="Nme3"/>
     <n v="50"/>
     <x v="1"/>
-    <s v="Pass"/>
+    <x v="0"/>
     <x v="2"/>
   </r>
   <r>
@@ -987,7 +1248,7 @@
     <s v="Nme4"/>
     <n v="82"/>
     <x v="3"/>
-    <s v="Pass"/>
+    <x v="0"/>
     <x v="2"/>
   </r>
   <r>
@@ -995,7 +1256,7 @@
     <s v="Nme5"/>
     <n v="94"/>
     <x v="3"/>
-    <s v="Pass"/>
+    <x v="0"/>
     <x v="2"/>
   </r>
   <r>
@@ -1003,7 +1264,7 @@
     <s v="Nme6"/>
     <n v="34"/>
     <x v="2"/>
-    <s v="Fail"/>
+    <x v="1"/>
     <x v="2"/>
   </r>
   <r>
@@ -1011,7 +1272,7 @@
     <s v="Nme7"/>
     <n v="12"/>
     <x v="2"/>
-    <s v="Fail"/>
+    <x v="1"/>
     <x v="2"/>
   </r>
   <r>
@@ -1019,7 +1280,7 @@
     <s v="Nme8"/>
     <n v="99"/>
     <x v="3"/>
-    <s v="Pass"/>
+    <x v="0"/>
     <x v="2"/>
   </r>
   <r>
@@ -1027,7 +1288,7 @@
     <s v="Nme9"/>
     <n v="54"/>
     <x v="1"/>
-    <s v="Pass"/>
+    <x v="0"/>
     <x v="2"/>
   </r>
   <r>
@@ -1035,15 +1296,15 @@
     <s v="Nme10"/>
     <n v="1"/>
     <x v="2"/>
-    <s v="Fail"/>
+    <x v="1"/>
     <x v="2"/>
   </r>
 </pivotCacheRecords>
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4205CF1B-8876-4A27-8D0D-37463B828738}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="L4:U9" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4205CF1B-8876-4A27-8D0D-37463B828738}" name="PivotTable1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="L4:W9" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="6">
     <pivotField axis="axisCol" showAll="0">
       <items count="11">
@@ -1064,14 +1325,20 @@
     <pivotField dataField="1" showAll="0"/>
     <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
       <items count="5">
-        <item h="1" x="2"/>
-        <item h="1" x="1"/>
+        <item x="2"/>
+        <item x="1"/>
         <item x="0"/>
         <item x="3"/>
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
     <pivotField axis="axisRow" numFmtId="14" showAll="0">
       <items count="4">
         <item x="2"/>
@@ -1101,7 +1368,7 @@
   <colFields count="1">
     <field x="0"/>
   </colFields>
-  <colItems count="9">
+  <colItems count="11">
     <i>
       <x/>
     </i>
@@ -1121,7 +1388,13 @@
       <x v="5"/>
     </i>
     <i>
+      <x v="6"/>
+    </i>
+    <i>
       <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
     </i>
     <i>
       <x v="9"/>
@@ -1137,7 +1410,7 @@
     <dataField name="Sum of Sales" fld="2" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="11">
+    <format dxfId="35">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="3" count="0"/>
@@ -1158,17 +1431,15 @@
 </file>
 
 <file path=xl/slicerCaches/slicerCache1.xml><?xml version="1.0" encoding="utf-8"?>
-<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_Class" xr10:uid="{690CFFD6-AF64-4EEE-B973-2EB0B2785A75}" sourceName="Class">
+<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_Result" xr10:uid="{08A7F22F-CF4E-4A77-BFDF-2826EEA44CCA}" sourceName="Result">
   <pivotTables>
     <pivotTable tabId="1" name="PivotTable1"/>
   </pivotTables>
   <data>
     <tabular pivotCacheId="1849779143">
-      <items count="4">
-        <i x="2"/>
-        <i x="1"/>
+      <items count="2">
+        <i x="1" s="1"/>
         <i x="0" s="1"/>
-        <i x="3" s="1"/>
       </items>
     </tabular>
   </data>
@@ -1176,6 +1447,24 @@
 </file>
 
 <file path=xl/slicerCaches/slicerCache2.xml><?xml version="1.0" encoding="utf-8"?>
+<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_Class" xr10:uid="{6D9B338B-B7B1-497B-8095-05BE9C672277}" sourceName="Class">
+  <pivotTables>
+    <pivotTable tabId="1" name="PivotTable1"/>
+  </pivotTables>
+  <data>
+    <tabular pivotCacheId="1849779143">
+      <items count="4">
+        <i x="3" s="1"/>
+        <i x="2" s="1"/>
+        <i x="0" s="1"/>
+        <i x="1" s="1"/>
+      </items>
+    </tabular>
+  </data>
+</slicerCacheDefinition>
+</file>
+
+<file path=xl/slicerCaches/slicerCache3.xml><?xml version="1.0" encoding="utf-8"?>
 <slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_Class1" xr10:uid="{DA21E646-043D-46D5-A563-43FE61993543}" sourceName="Class">
   <extLst>
     <x:ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{2F2917AC-EB37-4324-AD4E-5DD8C200BD13}">
@@ -1187,7 +1476,8 @@
 
 <file path=xl/slicers/slicer1.xml><?xml version="1.0" encoding="utf-8"?>
 <slicers xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10">
-  <slicer name="Class" xr10:uid="{4116A96A-6C7A-44A9-8738-E64D32944A2D}" cache="Slicer_Class" caption="Class" columnCount="4" rowHeight="241300"/>
+  <slicer name="Result" xr10:uid="{C3548829-FF81-4016-B199-6F396B04DCDD}" cache="Slicer_Result" caption="Result" columnCount="2" rowHeight="234950"/>
+  <slicer name="Class" xr10:uid="{1720AF81-C3AE-4430-996A-DEEC0C1003EA}" cache="Slicer_Class" caption="Class" columnCount="4" rowHeight="234950"/>
 </slicers>
 </file>
 
@@ -1198,27 +1488,19 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{41E3059B-4105-409A-98C7-A706C67FE6A3}" name="Table1" displayName="Table1" ref="A1:F31" totalsRowShown="0" headerRowDxfId="10" dataDxfId="8" headerRowBorderDxfId="9" tableBorderDxfId="7" totalsRowBorderDxfId="6">
-  <autoFilter ref="A1:F31" xr:uid="{41E3059B-4105-409A-98C7-A706C67FE6A3}">
-    <filterColumn colId="3">
-      <filters>
-        <filter val="Fail"/>
-        <filter val="First class"/>
-        <filter val="Pass"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{41E3059B-4105-409A-98C7-A706C67FE6A3}" name="Table1" displayName="Table1" ref="A1:F31" totalsRowShown="0" headerRowDxfId="34" dataDxfId="32" headerRowBorderDxfId="33" tableBorderDxfId="31" totalsRowBorderDxfId="30">
+  <autoFilter ref="A1:F31" xr:uid="{41E3059B-4105-409A-98C7-A706C67FE6A3}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{725CB17D-65FD-4272-A2F8-5A1BBCD45877}" name="Emp ID" dataDxfId="5"/>
-    <tableColumn id="2" xr3:uid="{D64749C1-E97B-482D-97EF-AF6E311D0951}" name="Name" dataDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{402A62F2-58F9-464B-97F7-C4B94AFC840F}" name="Sales" dataDxfId="3"/>
-    <tableColumn id="4" xr3:uid="{DB62E960-6436-4D67-B8BE-E8CDC61FF8E0}" name="Class" dataDxfId="2">
+    <tableColumn id="1" xr3:uid="{725CB17D-65FD-4272-A2F8-5A1BBCD45877}" name="Emp ID" dataDxfId="29"/>
+    <tableColumn id="2" xr3:uid="{D64749C1-E97B-482D-97EF-AF6E311D0951}" name="Name" dataDxfId="28"/>
+    <tableColumn id="3" xr3:uid="{402A62F2-58F9-464B-97F7-C4B94AFC840F}" name="Sales" dataDxfId="27"/>
+    <tableColumn id="4" xr3:uid="{DB62E960-6436-4D67-B8BE-E8CDC61FF8E0}" name="Class" dataDxfId="26">
       <calculatedColumnFormula>VLOOKUP($C2,Sheet1!$H$12:$I$15,2,1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{89C96C5C-7610-41C5-B2F4-5A56672103E2}" name="Result" dataDxfId="1">
+    <tableColumn id="5" xr3:uid="{89C96C5C-7610-41C5-B2F4-5A56672103E2}" name="Result" dataDxfId="25">
       <calculatedColumnFormula>IF(C2&gt;34,"Pass","Fail")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{B40B3498-A405-4F59-9F80-318E8ACB7ABD}" name="Date" dataDxfId="0"/>
+    <tableColumn id="6" xr3:uid="{B40B3498-A405-4F59-9F80-318E8ACB7ABD}" name="Date" dataDxfId="24"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1521,24 +1803,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41D7F216-80C1-4E05-9911-849580BAC999}">
-  <dimension ref="A1:U31"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:W31"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="4" max="4" width="10.453125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.08984375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.36328125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.26953125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="6.7265625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="5.7265625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.36328125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="16.453125" bestFit="1" customWidth="1"/>
-    <col min="14" max="20" width="4.81640625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.7265625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="4.81640625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="10.7265625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.21875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="22" width="5" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="10.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
@@ -1558,7 +1838,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A2" s="13">
         <v>1001</v>
       </c>
@@ -1578,7 +1858,7 @@
       </c>
       <c r="F2" s="4">
         <f ca="1">TODAY()</f>
-        <v>45768</v>
+        <v>45925</v>
       </c>
       <c r="I2" s="11"/>
       <c r="L2" s="8" t="s">
@@ -1588,7 +1868,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A3" s="13">
         <v>1002</v>
       </c>
@@ -1608,10 +1888,10 @@
       </c>
       <c r="F3" s="4">
         <f t="shared" ref="F3:F11" ca="1" si="2">TODAY()</f>
-        <v>45768</v>
-      </c>
-    </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.35">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A4" s="13">
         <v>1003</v>
       </c>
@@ -1631,7 +1911,7 @@
       </c>
       <c r="F4" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>45768</v>
+        <v>45925</v>
       </c>
       <c r="L4" s="8" t="s">
         <v>15</v>
@@ -1640,7 +1920,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A5" s="13">
         <v>1004</v>
       </c>
@@ -1660,7 +1940,7 @@
       </c>
       <c r="F5" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>45768</v>
+        <v>45925</v>
       </c>
       <c r="L5" s="8" t="s">
         <v>16</v>
@@ -1684,16 +1964,22 @@
         <v>1006</v>
       </c>
       <c r="S5">
+        <v>1007</v>
+      </c>
+      <c r="T5">
         <v>1008</v>
       </c>
-      <c r="T5">
+      <c r="U5">
+        <v>1009</v>
+      </c>
+      <c r="V5">
         <v>1010</v>
       </c>
-      <c r="U5" t="s">
+      <c r="W5" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A6" s="13">
         <v>1005</v>
       </c>
@@ -1713,28 +1999,46 @@
       </c>
       <c r="F6" s="4">
         <f ca="1">TODAY()</f>
-        <v>45768</v>
+        <v>45925</v>
       </c>
       <c r="L6" s="9">
         <v>45644</v>
       </c>
-      <c r="N6">
+      <c r="M6" s="25">
+        <v>47</v>
+      </c>
+      <c r="N6" s="25">
         <v>92</v>
       </c>
-      <c r="P6">
+      <c r="O6" s="25">
+        <v>50</v>
+      </c>
+      <c r="P6" s="25">
         <v>82</v>
       </c>
-      <c r="Q6">
+      <c r="Q6" s="25">
         <v>94</v>
       </c>
-      <c r="S6">
+      <c r="R6" s="25">
+        <v>34</v>
+      </c>
+      <c r="S6" s="25">
+        <v>12</v>
+      </c>
+      <c r="T6" s="25">
         <v>99</v>
       </c>
-      <c r="U6">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="U6" s="25">
+        <v>54</v>
+      </c>
+      <c r="V6" s="25">
+        <v>1</v>
+      </c>
+      <c r="W6" s="25">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A7" s="13">
         <v>1006</v>
       </c>
@@ -1754,37 +2058,46 @@
       </c>
       <c r="F7" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>45768</v>
+        <v>45925</v>
       </c>
       <c r="L7" s="9">
         <v>45645</v>
       </c>
-      <c r="M7">
+      <c r="M7" s="25">
         <v>96</v>
       </c>
-      <c r="N7">
+      <c r="N7" s="25">
         <v>87</v>
       </c>
-      <c r="O7">
+      <c r="O7" s="25">
         <v>100</v>
       </c>
-      <c r="P7">
+      <c r="P7" s="25">
         <v>86</v>
       </c>
-      <c r="Q7">
+      <c r="Q7" s="25">
         <v>85</v>
       </c>
-      <c r="R7">
+      <c r="R7" s="25">
         <v>75</v>
       </c>
-      <c r="S7">
+      <c r="S7" s="25">
+        <v>3</v>
+      </c>
+      <c r="T7" s="25">
         <v>100</v>
       </c>
-      <c r="U7">
-        <v>629</v>
-      </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="U7" s="25">
+        <v>59</v>
+      </c>
+      <c r="V7" s="25">
+        <v>3</v>
+      </c>
+      <c r="W7" s="25">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A8" s="13">
         <v>1007</v>
       </c>
@@ -1804,25 +2117,46 @@
       </c>
       <c r="F8" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>45768</v>
+        <v>45925</v>
       </c>
       <c r="L8" s="9">
         <v>45646</v>
       </c>
-      <c r="M8">
+      <c r="M8" s="25">
         <v>61</v>
       </c>
-      <c r="S8">
+      <c r="N8" s="25">
+        <v>37</v>
+      </c>
+      <c r="O8" s="25">
+        <v>12</v>
+      </c>
+      <c r="P8" s="25">
+        <v>11</v>
+      </c>
+      <c r="Q8" s="25">
+        <v>45</v>
+      </c>
+      <c r="R8" s="25">
+        <v>6</v>
+      </c>
+      <c r="S8" s="25">
+        <v>19</v>
+      </c>
+      <c r="T8" s="25">
         <v>87</v>
       </c>
-      <c r="T8">
+      <c r="U8" s="25">
+        <v>43</v>
+      </c>
+      <c r="V8" s="25">
         <v>68</v>
       </c>
-      <c r="U8">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="W8" s="25">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A9" s="13">
         <v>1008</v>
       </c>
@@ -1842,40 +2176,46 @@
       </c>
       <c r="F9" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>45768</v>
+        <v>45925</v>
       </c>
       <c r="L9" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="M9">
-        <v>157</v>
-      </c>
-      <c r="N9">
+      <c r="M9" s="25">
+        <v>204</v>
+      </c>
+      <c r="N9" s="25">
+        <v>216</v>
+      </c>
+      <c r="O9" s="25">
+        <v>162</v>
+      </c>
+      <c r="P9" s="25">
         <v>179</v>
       </c>
-      <c r="O9">
-        <v>100</v>
-      </c>
-      <c r="P9">
-        <v>168</v>
-      </c>
-      <c r="Q9">
-        <v>179</v>
-      </c>
-      <c r="R9">
-        <v>75</v>
-      </c>
-      <c r="S9">
+      <c r="Q9" s="25">
+        <v>224</v>
+      </c>
+      <c r="R9" s="25">
+        <v>115</v>
+      </c>
+      <c r="S9" s="25">
+        <v>34</v>
+      </c>
+      <c r="T9" s="25">
         <v>286</v>
       </c>
-      <c r="T9">
-        <v>68</v>
-      </c>
-      <c r="U9">
-        <v>1212</v>
-      </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="U9" s="25">
+        <v>156</v>
+      </c>
+      <c r="V9" s="25">
+        <v>72</v>
+      </c>
+      <c r="W9" s="25">
+        <v>1648</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A10" s="13">
         <v>1009</v>
       </c>
@@ -1895,10 +2235,10 @@
       </c>
       <c r="F10" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>45768</v>
-      </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.35">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A11" s="13">
         <v>1010</v>
       </c>
@@ -1918,10 +2258,10 @@
       </c>
       <c r="F11" s="4">
         <f t="shared" ca="1" si="2"/>
-        <v>45768</v>
-      </c>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.35">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A12" s="13">
         <v>1001</v>
       </c>
@@ -1941,7 +2281,7 @@
       </c>
       <c r="F12" s="5">
         <f ca="1">F2-1</f>
-        <v>45767</v>
+        <v>45924</v>
       </c>
       <c r="H12">
         <v>0</v>
@@ -1950,7 +2290,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A13" s="13">
         <v>1002</v>
       </c>
@@ -1970,7 +2310,7 @@
       </c>
       <c r="F13" s="5">
         <f t="shared" ref="F13:F31" ca="1" si="3">F3-1</f>
-        <v>45767</v>
+        <v>45924</v>
       </c>
       <c r="H13">
         <v>35</v>
@@ -1979,7 +2319,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A14" s="13">
         <v>1003</v>
       </c>
@@ -1999,7 +2339,7 @@
       </c>
       <c r="F14" s="5">
         <f t="shared" ca="1" si="3"/>
-        <v>45767</v>
+        <v>45924</v>
       </c>
       <c r="H14">
         <v>60</v>
@@ -2008,7 +2348,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A15" s="13">
         <v>1004</v>
       </c>
@@ -2028,7 +2368,7 @@
       </c>
       <c r="F15" s="5">
         <f t="shared" ca="1" si="3"/>
-        <v>45767</v>
+        <v>45924</v>
       </c>
       <c r="H15">
         <v>75</v>
@@ -2037,7 +2377,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A16" s="13">
         <v>1005</v>
       </c>
@@ -2057,10 +2397,10 @@
       </c>
       <c r="F16" s="5">
         <f t="shared" ca="1" si="3"/>
-        <v>45767</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+        <v>45924</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="13">
         <v>1006</v>
       </c>
@@ -2080,10 +2420,10 @@
       </c>
       <c r="F17" s="5">
         <f t="shared" ca="1" si="3"/>
-        <v>45767</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+        <v>45924</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="13">
         <v>1007</v>
       </c>
@@ -2103,10 +2443,10 @@
       </c>
       <c r="F18" s="5">
         <f t="shared" ca="1" si="3"/>
-        <v>45767</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+        <v>45924</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="13">
         <v>1008</v>
       </c>
@@ -2126,10 +2466,10 @@
       </c>
       <c r="F19" s="5">
         <f t="shared" ca="1" si="3"/>
-        <v>45767</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+        <v>45924</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="13">
         <v>1009</v>
       </c>
@@ -2149,10 +2489,10 @@
       </c>
       <c r="F20" s="5">
         <f t="shared" ca="1" si="3"/>
-        <v>45767</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+        <v>45924</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="13">
         <v>1010</v>
       </c>
@@ -2172,10 +2512,10 @@
       </c>
       <c r="F21" s="5">
         <f t="shared" ca="1" si="3"/>
-        <v>45767</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+        <v>45924</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="6">
         <v>1001</v>
       </c>
@@ -2195,10 +2535,10 @@
       </c>
       <c r="F22" s="7">
         <f t="shared" ca="1" si="3"/>
-        <v>45766</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+        <v>45923</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="6">
         <v>1002</v>
       </c>
@@ -2218,10 +2558,10 @@
       </c>
       <c r="F23" s="7">
         <f t="shared" ca="1" si="3"/>
-        <v>45766</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+        <v>45923</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="6">
         <v>1003</v>
       </c>
@@ -2241,10 +2581,10 @@
       </c>
       <c r="F24" s="7">
         <f t="shared" ca="1" si="3"/>
-        <v>45766</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+        <v>45923</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="6">
         <v>1004</v>
       </c>
@@ -2264,10 +2604,10 @@
       </c>
       <c r="F25" s="7">
         <f t="shared" ca="1" si="3"/>
-        <v>45766</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+        <v>45923</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="6">
         <v>1005</v>
       </c>
@@ -2287,10 +2627,10 @@
       </c>
       <c r="F26" s="7">
         <f t="shared" ca="1" si="3"/>
-        <v>45766</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+        <v>45923</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="6">
         <v>1006</v>
       </c>
@@ -2310,10 +2650,10 @@
       </c>
       <c r="F27" s="7">
         <f t="shared" ca="1" si="3"/>
-        <v>45766</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+        <v>45923</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="6">
         <v>1007</v>
       </c>
@@ -2333,10 +2673,10 @@
       </c>
       <c r="F28" s="7">
         <f t="shared" ca="1" si="3"/>
-        <v>45766</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+        <v>45923</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="6">
         <v>1008</v>
       </c>
@@ -2356,10 +2696,10 @@
       </c>
       <c r="F29" s="7">
         <f t="shared" ca="1" si="3"/>
-        <v>45766</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+        <v>45923</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" s="6">
         <v>1009</v>
       </c>
@@ -2379,10 +2719,10 @@
       </c>
       <c r="F30" s="7">
         <f t="shared" ca="1" si="3"/>
-        <v>45766</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+        <v>45923</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="6">
         <v>1010</v>
       </c>
@@ -2402,7 +2742,7 @@
       </c>
       <c r="F31" s="7">
         <f t="shared" ca="1" si="3"/>
-        <v>45766</v>
+        <v>45923</v>
       </c>
     </row>
   </sheetData>
@@ -2422,14 +2762,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{753B0B39-50F7-4298-A684-C9AAB7E9639F}">
   <dimension ref="A1:F31"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.81640625" customWidth="1"/>
-    <col min="4" max="4" width="10.453125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.08984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.77734375" customWidth="1"/>
+    <col min="4" max="4" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
@@ -2449,7 +2789,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="16">
         <v>1001</v>
       </c>
@@ -2469,10 +2809,10 @@
       </c>
       <c r="F2" s="17">
         <f ca="1">TODAY()</f>
-        <v>45768</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="16">
         <v>1002</v>
       </c>
@@ -2492,10 +2832,10 @@
       </c>
       <c r="F3" s="17">
         <f t="shared" ref="F3:F11" ca="1" si="1">TODAY()</f>
-        <v>45768</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="16">
         <v>1003</v>
       </c>
@@ -2515,10 +2855,10 @@
       </c>
       <c r="F4" s="17">
         <f t="shared" ca="1" si="1"/>
-        <v>45768</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="16">
         <v>1004</v>
       </c>
@@ -2538,10 +2878,10 @@
       </c>
       <c r="F5" s="17">
         <f t="shared" ca="1" si="1"/>
-        <v>45768</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="16">
         <v>1005</v>
       </c>
@@ -2561,10 +2901,10 @@
       </c>
       <c r="F6" s="17">
         <f ca="1">TODAY()</f>
-        <v>45768</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="16">
         <v>1006</v>
       </c>
@@ -2584,10 +2924,10 @@
       </c>
       <c r="F7" s="17">
         <f t="shared" ca="1" si="1"/>
-        <v>45768</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="16">
         <v>1007</v>
       </c>
@@ -2607,10 +2947,10 @@
       </c>
       <c r="F8" s="17">
         <f t="shared" ca="1" si="1"/>
-        <v>45768</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="16">
         <v>1008</v>
       </c>
@@ -2630,10 +2970,10 @@
       </c>
       <c r="F9" s="17">
         <f t="shared" ca="1" si="1"/>
-        <v>45768</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="16">
         <v>1009</v>
       </c>
@@ -2653,10 +2993,10 @@
       </c>
       <c r="F10" s="17">
         <f t="shared" ca="1" si="1"/>
-        <v>45768</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="16">
         <v>1010</v>
       </c>
@@ -2676,10 +3016,10 @@
       </c>
       <c r="F11" s="17">
         <f t="shared" ca="1" si="1"/>
-        <v>45768</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="16">
         <v>1001</v>
       </c>
@@ -2699,10 +3039,10 @@
       </c>
       <c r="F12" s="17">
         <f ca="1">F2-1</f>
-        <v>45767</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+        <v>45924</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="16">
         <v>1002</v>
       </c>
@@ -2722,10 +3062,10 @@
       </c>
       <c r="F13" s="17">
         <f t="shared" ref="F13:F31" ca="1" si="2">F3-1</f>
-        <v>45767</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+        <v>45924</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="16">
         <v>1003</v>
       </c>
@@ -2745,10 +3085,10 @@
       </c>
       <c r="F14" s="17">
         <f t="shared" ca="1" si="2"/>
-        <v>45767</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+        <v>45924</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="16">
         <v>1004</v>
       </c>
@@ -2768,10 +3108,10 @@
       </c>
       <c r="F15" s="17">
         <f t="shared" ca="1" si="2"/>
-        <v>45767</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+        <v>45924</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="16">
         <v>1005</v>
       </c>
@@ -2791,10 +3131,10 @@
       </c>
       <c r="F16" s="17">
         <f t="shared" ca="1" si="2"/>
-        <v>45767</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+        <v>45924</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="16">
         <v>1006</v>
       </c>
@@ -2814,10 +3154,10 @@
       </c>
       <c r="F17" s="17">
         <f t="shared" ca="1" si="2"/>
-        <v>45767</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+        <v>45924</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="16">
         <v>1007</v>
       </c>
@@ -2837,10 +3177,10 @@
       </c>
       <c r="F18" s="17">
         <f t="shared" ca="1" si="2"/>
-        <v>45767</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+        <v>45924</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="16">
         <v>1008</v>
       </c>
@@ -2860,10 +3200,10 @@
       </c>
       <c r="F19" s="17">
         <f t="shared" ca="1" si="2"/>
-        <v>45767</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+        <v>45924</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="16">
         <v>1009</v>
       </c>
@@ -2883,10 +3223,10 @@
       </c>
       <c r="F20" s="17">
         <f t="shared" ca="1" si="2"/>
-        <v>45767</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+        <v>45924</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="16">
         <v>1010</v>
       </c>
@@ -2906,10 +3246,10 @@
       </c>
       <c r="F21" s="17">
         <f t="shared" ca="1" si="2"/>
-        <v>45767</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+        <v>45924</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="16">
         <v>1001</v>
       </c>
@@ -2929,10 +3269,10 @@
       </c>
       <c r="F22" s="17">
         <f t="shared" ca="1" si="2"/>
-        <v>45766</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+        <v>45923</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="16">
         <v>1002</v>
       </c>
@@ -2952,10 +3292,10 @@
       </c>
       <c r="F23" s="17">
         <f t="shared" ca="1" si="2"/>
-        <v>45766</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+        <v>45923</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="16">
         <v>1003</v>
       </c>
@@ -2975,10 +3315,10 @@
       </c>
       <c r="F24" s="17">
         <f t="shared" ca="1" si="2"/>
-        <v>45766</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+        <v>45923</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="16">
         <v>1004</v>
       </c>
@@ -2998,10 +3338,10 @@
       </c>
       <c r="F25" s="17">
         <f t="shared" ca="1" si="2"/>
-        <v>45766</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+        <v>45923</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="16">
         <v>1005</v>
       </c>
@@ -3021,10 +3361,10 @@
       </c>
       <c r="F26" s="17">
         <f t="shared" ca="1" si="2"/>
-        <v>45766</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+        <v>45923</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="16">
         <v>1006</v>
       </c>
@@ -3044,10 +3384,10 @@
       </c>
       <c r="F27" s="17">
         <f t="shared" ca="1" si="2"/>
-        <v>45766</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+        <v>45923</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="16">
         <v>1007</v>
       </c>
@@ -3067,10 +3407,10 @@
       </c>
       <c r="F28" s="17">
         <f t="shared" ca="1" si="2"/>
-        <v>45766</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+        <v>45923</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="16">
         <v>1008</v>
       </c>
@@ -3090,10 +3430,10 @@
       </c>
       <c r="F29" s="17">
         <f t="shared" ca="1" si="2"/>
-        <v>45766</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+        <v>45923</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" s="16">
         <v>1009</v>
       </c>
@@ -3113,10 +3453,10 @@
       </c>
       <c r="F30" s="17">
         <f t="shared" ca="1" si="2"/>
-        <v>45766</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+        <v>45923</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="21">
         <v>1010</v>
       </c>
@@ -3136,7 +3476,7 @@
       </c>
       <c r="F31" s="24">
         <f t="shared" ca="1" si="2"/>
-        <v>45766</v>
+        <v>45923</v>
       </c>
     </row>
   </sheetData>
